--- a/output/yearly_total_coral_cover_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_20_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.266166331925235</v>
+        <v>1.257094983137995</v>
       </c>
       <c r="C3" t="n">
-        <v>4.604845282678543</v>
+        <v>4.596706594210337</v>
       </c>
       <c r="D3" t="n">
-        <v>6.083316294745139</v>
+        <v>6.04314317868736</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95432790934892</v>
+        <v>11.89694475603569</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.404110904581553</v>
+        <v>1.385997715813579</v>
       </c>
       <c r="C4" t="n">
-        <v>5.038397966994056</v>
+        <v>5.040177535475037</v>
       </c>
       <c r="D4" t="n">
-        <v>6.332317809257439</v>
+        <v>6.30425080402272</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77482668083305</v>
+        <v>12.73042605531134</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.594930677014325</v>
+        <v>1.563092769662611</v>
       </c>
       <c r="C5" t="n">
-        <v>5.583194699222116</v>
+        <v>5.571887468106786</v>
       </c>
       <c r="D5" t="n">
-        <v>6.617957770474056</v>
+        <v>6.54933777555796</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7960831467105</v>
+        <v>13.68431801332736</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.815663766031351</v>
+        <v>1.772127561703599</v>
       </c>
       <c r="C6" t="n">
-        <v>6.237476651308875</v>
+        <v>6.193406740194049</v>
       </c>
       <c r="D6" t="n">
-        <v>7.074578000112131</v>
+        <v>6.869219270739869</v>
       </c>
       <c r="E6" t="n">
-        <v>15.12771841745236</v>
+        <v>14.83475357263752</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.073458657740996</v>
+        <v>2.016525889494562</v>
       </c>
       <c r="C7" t="n">
-        <v>6.991773750445486</v>
+        <v>6.924700275551416</v>
       </c>
       <c r="D7" t="n">
-        <v>7.453635727234233</v>
+        <v>7.219284138414948</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51886813542072</v>
+        <v>16.16051030346092</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.317480342744717</v>
+        <v>1.259105760413184</v>
       </c>
       <c r="C8" t="n">
-        <v>4.653402425385205</v>
+        <v>4.539708064314294</v>
       </c>
       <c r="D8" t="n">
-        <v>5.655390384802347</v>
+        <v>5.470736015602061</v>
       </c>
       <c r="E8" t="n">
-        <v>11.62627315293227</v>
+        <v>11.26954984032954</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.696307889887304</v>
+        <v>1.602478206001732</v>
       </c>
       <c r="C9" t="n">
-        <v>5.693246040941125</v>
+        <v>5.478526021934559</v>
       </c>
       <c r="D9" t="n">
-        <v>6.151868599399081</v>
+        <v>5.947677481499072</v>
       </c>
       <c r="E9" t="n">
-        <v>13.54142253022751</v>
+        <v>13.02868170943536</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.10308107833164</v>
+        <v>1.979424702240737</v>
       </c>
       <c r="C10" t="n">
-        <v>6.905553613687156</v>
+        <v>6.59021909922556</v>
       </c>
       <c r="D10" t="n">
-        <v>6.706829857764379</v>
+        <v>6.489347853578607</v>
       </c>
       <c r="E10" t="n">
-        <v>15.71546454978317</v>
+        <v>15.05899165504491</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.523268112350814</v>
+        <v>2.37119940463098</v>
       </c>
       <c r="C11" t="n">
-        <v>8.239566679131185</v>
+        <v>7.834806632897125</v>
       </c>
       <c r="D11" t="n">
-        <v>7.191585185838451</v>
+        <v>7.06307524292515</v>
       </c>
       <c r="E11" t="n">
-        <v>17.95441997732045</v>
+        <v>17.26908128045326</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.939036624350002</v>
+        <v>2.778485354123907</v>
       </c>
       <c r="C12" t="n">
-        <v>9.734580845963803</v>
+        <v>9.159508231478991</v>
       </c>
       <c r="D12" t="n">
-        <v>7.624189008324727</v>
+        <v>7.551041219170071</v>
       </c>
       <c r="E12" t="n">
-        <v>20.29780647863853</v>
+        <v>19.48903480477297</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.35985389357492</v>
+        <v>3.196158461316023</v>
       </c>
       <c r="C13" t="n">
-        <v>11.30642214591464</v>
+        <v>10.51731112147724</v>
       </c>
       <c r="D13" t="n">
-        <v>8.075832047894627</v>
+        <v>8.036659482553342</v>
       </c>
       <c r="E13" t="n">
-        <v>22.74210808738419</v>
+        <v>21.7501290653466</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.928702269855114</v>
+        <v>1.852479378097392</v>
       </c>
       <c r="C14" t="n">
-        <v>7.984053387310142</v>
+        <v>7.409141931703211</v>
       </c>
       <c r="D14" t="n">
-        <v>6.121363833088584</v>
+        <v>6.147969195873674</v>
       </c>
       <c r="E14" t="n">
-        <v>16.03411949025384</v>
+        <v>15.40959050567428</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.012347174256942</v>
+        <v>1.940797401571435</v>
       </c>
       <c r="C15" t="n">
-        <v>8.7461743126399</v>
+        <v>7.918983149472665</v>
       </c>
       <c r="D15" t="n">
-        <v>6.114147987462371</v>
+        <v>6.170421765869798</v>
       </c>
       <c r="E15" t="n">
-        <v>16.87266947435921</v>
+        <v>16.0302023169139</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.369860418235461</v>
+        <v>2.316433708170349</v>
       </c>
       <c r="C16" t="n">
-        <v>10.49286055812765</v>
+        <v>9.339071386188632</v>
       </c>
       <c r="D16" t="n">
-        <v>6.564171317612067</v>
+        <v>6.743801695058105</v>
       </c>
       <c r="E16" t="n">
-        <v>19.42689229397518</v>
+        <v>18.39930678941709</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.922811783629633</v>
+        <v>1.906789661096325</v>
       </c>
       <c r="C17" t="n">
-        <v>9.85826865957956</v>
+        <v>8.656049873390042</v>
       </c>
       <c r="D17" t="n">
-        <v>6.059229020886804</v>
+        <v>6.301200377552516</v>
       </c>
       <c r="E17" t="n">
-        <v>17.840309464096</v>
+        <v>16.86403991203888</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.219584297146401</v>
+        <v>2.226927769974168</v>
       </c>
       <c r="C18" t="n">
-        <v>11.60652570139411</v>
+        <v>10.08953896626898</v>
       </c>
       <c r="D18" t="n">
-        <v>6.40607066732016</v>
+        <v>6.799005368467903</v>
       </c>
       <c r="E18" t="n">
-        <v>20.23218066586067</v>
+        <v>19.11547210471105</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.250224642995944</v>
+        <v>2.278597151648678</v>
       </c>
       <c r="C19" t="n">
-        <v>12.52513721078081</v>
+        <v>10.79427673828551</v>
       </c>
       <c r="D19" t="n">
-        <v>6.475499864964493</v>
+        <v>6.944559283099536</v>
       </c>
       <c r="E19" t="n">
-        <v>21.25086171874124</v>
+        <v>20.01743317303372</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.522571273631052</v>
+        <v>2.579826799742726</v>
       </c>
       <c r="C20" t="n">
-        <v>14.46279301969865</v>
+        <v>12.44026512174867</v>
       </c>
       <c r="D20" t="n">
-        <v>6.817364050537319</v>
+        <v>7.409141931703211</v>
       </c>
       <c r="E20" t="n">
-        <v>23.80272834386702</v>
+        <v>22.42923385319461</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.510477747845973</v>
+        <v>1.553792456557342</v>
       </c>
       <c r="C21" t="n">
-        <v>10.65591903432601</v>
+        <v>9.207625186067029</v>
       </c>
       <c r="D21" t="n">
-        <v>5.640827784290898</v>
+        <v>6.204380418959695</v>
       </c>
       <c r="E21" t="n">
-        <v>17.80722456646288</v>
+        <v>16.96579806158407</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_20_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257094983137995</v>
+        <v>1.250684170629263</v>
       </c>
       <c r="C3" t="n">
-        <v>4.596706594210337</v>
+        <v>4.674529734725982</v>
       </c>
       <c r="D3" t="n">
-        <v>6.04314317868736</v>
+        <v>6.1001827203041</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89694475603569</v>
+        <v>12.02539662565935</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.385997715813579</v>
+        <v>1.361549764072811</v>
       </c>
       <c r="C4" t="n">
-        <v>5.040177535475037</v>
+        <v>5.296199974544759</v>
       </c>
       <c r="D4" t="n">
-        <v>6.30425080402272</v>
+        <v>6.382503317191868</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73042605531134</v>
+        <v>13.04025305580944</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.563092769662611</v>
+        <v>1.51877100807572</v>
       </c>
       <c r="C5" t="n">
-        <v>5.571887468106786</v>
+        <v>6.120499338270028</v>
       </c>
       <c r="D5" t="n">
-        <v>6.54933777555796</v>
+        <v>6.806459405826173</v>
       </c>
       <c r="E5" t="n">
-        <v>13.68431801332736</v>
+        <v>14.44572975217192</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.772127561703599</v>
+        <v>1.707887059932487</v>
       </c>
       <c r="C6" t="n">
-        <v>6.193406740194049</v>
+        <v>7.180741095281637</v>
       </c>
       <c r="D6" t="n">
-        <v>6.869219270739869</v>
+        <v>7.204653573314783</v>
       </c>
       <c r="E6" t="n">
-        <v>14.83475357263752</v>
+        <v>16.09328172852891</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.016525889494562</v>
+        <v>1.92007814876491</v>
       </c>
       <c r="C7" t="n">
-        <v>6.924700275551416</v>
+        <v>8.403159788282185</v>
       </c>
       <c r="D7" t="n">
-        <v>7.219284138414948</v>
+        <v>7.632861139798002</v>
       </c>
       <c r="E7" t="n">
-        <v>16.16051030346092</v>
+        <v>17.9560990768451</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.259105760413184</v>
+        <v>1.157800378193457</v>
       </c>
       <c r="C8" t="n">
-        <v>4.539708064314294</v>
+        <v>6.046434833939997</v>
       </c>
       <c r="D8" t="n">
-        <v>5.470736015602061</v>
+        <v>5.832562976639603</v>
       </c>
       <c r="E8" t="n">
-        <v>11.26954984032954</v>
+        <v>13.03679818877306</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.602478206001732</v>
+        <v>1.428041120551498</v>
       </c>
       <c r="C9" t="n">
-        <v>5.478526021934559</v>
+        <v>7.464900476556104</v>
       </c>
       <c r="D9" t="n">
-        <v>5.947677481499072</v>
+        <v>6.349851430609814</v>
       </c>
       <c r="E9" t="n">
-        <v>13.02868170943536</v>
+        <v>15.24279302771742</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.979424702240737</v>
+        <v>1.709360650682955</v>
       </c>
       <c r="C10" t="n">
-        <v>6.59021909922556</v>
+        <v>9.013470037843097</v>
       </c>
       <c r="D10" t="n">
-        <v>6.489347853578607</v>
+        <v>6.841598888913481</v>
       </c>
       <c r="E10" t="n">
-        <v>15.05899165504491</v>
+        <v>17.56442957743953</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.37119940463098</v>
+        <v>1.979131747531131</v>
       </c>
       <c r="C11" t="n">
-        <v>7.834806632897125</v>
+        <v>10.61036057058638</v>
       </c>
       <c r="D11" t="n">
-        <v>7.06307524292515</v>
+        <v>7.362918347896128</v>
       </c>
       <c r="E11" t="n">
-        <v>17.26908128045326</v>
+        <v>19.95241066601364</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.778485354123907</v>
+        <v>2.242416856287321</v>
       </c>
       <c r="C12" t="n">
-        <v>9.159508231478991</v>
+        <v>12.23309420350492</v>
       </c>
       <c r="D12" t="n">
-        <v>7.551041219170071</v>
+        <v>7.882255168208707</v>
       </c>
       <c r="E12" t="n">
-        <v>19.48903480477297</v>
+        <v>22.35776622800095</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.196158461316023</v>
+        <v>2.496182841995062</v>
       </c>
       <c r="C13" t="n">
-        <v>10.51731112147724</v>
+        <v>13.88413290469927</v>
       </c>
       <c r="D13" t="n">
-        <v>8.036659482553342</v>
+        <v>8.306129176852318</v>
       </c>
       <c r="E13" t="n">
-        <v>21.7501290653466</v>
+        <v>24.68644492354665</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.852479378097392</v>
+        <v>1.433135663705409</v>
       </c>
       <c r="C14" t="n">
-        <v>7.409141931703211</v>
+        <v>9.699451333463552</v>
       </c>
       <c r="D14" t="n">
-        <v>6.147969195873674</v>
+        <v>6.293847087247706</v>
       </c>
       <c r="E14" t="n">
-        <v>15.40959050567428</v>
+        <v>17.42643408441667</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.940797401571435</v>
+        <v>1.456785965900715</v>
       </c>
       <c r="C15" t="n">
-        <v>7.918983149472665</v>
+        <v>10.35134162656048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.170421765869798</v>
+        <v>6.290577867392565</v>
       </c>
       <c r="E15" t="n">
-        <v>16.0302023169139</v>
+        <v>18.09870545985376</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.316433708170349</v>
+        <v>1.687575216215055</v>
       </c>
       <c r="C16" t="n">
-        <v>9.339071386188632</v>
+        <v>12.08520624703077</v>
       </c>
       <c r="D16" t="n">
-        <v>6.743801695058105</v>
+        <v>6.767010210786499</v>
       </c>
       <c r="E16" t="n">
-        <v>18.39930678941709</v>
+        <v>20.53979167403232</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.906789661096325</v>
+        <v>1.357904337128976</v>
       </c>
       <c r="C17" t="n">
-        <v>8.656049873390042</v>
+        <v>10.92864854656577</v>
       </c>
       <c r="D17" t="n">
-        <v>6.301200377552516</v>
+        <v>6.284451761718066</v>
       </c>
       <c r="E17" t="n">
-        <v>16.86403991203888</v>
+        <v>18.57100464541281</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.226927769974168</v>
+        <v>1.547352191617483</v>
       </c>
       <c r="C18" t="n">
-        <v>10.08953896626898</v>
+        <v>12.61669500167887</v>
       </c>
       <c r="D18" t="n">
-        <v>6.799005368467903</v>
+        <v>6.683188591797907</v>
       </c>
       <c r="E18" t="n">
-        <v>19.11547210471105</v>
+        <v>20.84723578509426</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.278597151648678</v>
+        <v>1.550209077436841</v>
       </c>
       <c r="C19" t="n">
-        <v>10.79427673828551</v>
+        <v>13.38189861479996</v>
       </c>
       <c r="D19" t="n">
-        <v>6.944559283099536</v>
+        <v>6.777298926727006</v>
       </c>
       <c r="E19" t="n">
-        <v>20.01743317303372</v>
+        <v>21.7094066189638</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.579826799742726</v>
+        <v>1.72057175655479</v>
       </c>
       <c r="C20" t="n">
-        <v>12.44026512174867</v>
+        <v>15.23491795413468</v>
       </c>
       <c r="D20" t="n">
-        <v>7.409141931703211</v>
+        <v>7.213410891907523</v>
       </c>
       <c r="E20" t="n">
-        <v>22.42923385319461</v>
+        <v>24.168900602597</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.553792456557342</v>
+        <v>1.020654365766112</v>
       </c>
       <c r="C21" t="n">
-        <v>9.207625186067029</v>
+        <v>11.11503334821703</v>
       </c>
       <c r="D21" t="n">
-        <v>6.204380418959695</v>
+        <v>6.018525761068732</v>
       </c>
       <c r="E21" t="n">
-        <v>16.96579806158407</v>
+        <v>18.15421347505188</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_20_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_20_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250684170629263</v>
+        <v>2.587474136242338</v>
       </c>
       <c r="C3" t="n">
-        <v>4.674529734725982</v>
+        <v>7.772817720620904</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1001827203041</v>
+        <v>8.177985633864479</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02539662565935</v>
+        <v>18.53827749072772</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.361549764072811</v>
+        <v>1.070218538201579</v>
       </c>
       <c r="C4" t="n">
-        <v>5.296199974544759</v>
+        <v>4.670554430680785</v>
       </c>
       <c r="D4" t="n">
-        <v>6.382503317191868</v>
+        <v>5.768071819628197</v>
       </c>
       <c r="E4" t="n">
-        <v>13.04025305580944</v>
+        <v>11.50884478851056</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.51877100807572</v>
+        <v>1.172042473944607</v>
       </c>
       <c r="C5" t="n">
-        <v>6.120499338270028</v>
+        <v>5.541183556358721</v>
       </c>
       <c r="D5" t="n">
-        <v>6.806459405826173</v>
+        <v>6.087708096606778</v>
       </c>
       <c r="E5" t="n">
-        <v>14.44572975217192</v>
+        <v>12.80093412691011</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.707887059932487</v>
+        <v>1.278918643000022</v>
       </c>
       <c r="C6" t="n">
-        <v>7.180741095281637</v>
+        <v>6.636831460968951</v>
       </c>
       <c r="D6" t="n">
-        <v>7.204653573314783</v>
+        <v>6.485480284737286</v>
       </c>
       <c r="E6" t="n">
-        <v>16.09328172852891</v>
+        <v>14.40123038870626</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.92007814876491</v>
+        <v>1.380598186500674</v>
       </c>
       <c r="C7" t="n">
-        <v>8.403159788282185</v>
+        <v>7.918063719666637</v>
       </c>
       <c r="D7" t="n">
-        <v>7.632861139798002</v>
+        <v>6.909883078911751</v>
       </c>
       <c r="E7" t="n">
-        <v>17.9560990768451</v>
+        <v>16.20854498507906</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.157800378193457</v>
+        <v>1.4813722391908</v>
       </c>
       <c r="C8" t="n">
-        <v>6.046434833939997</v>
+        <v>9.366562863408442</v>
       </c>
       <c r="D8" t="n">
-        <v>5.832562976639603</v>
+        <v>7.301275684762289</v>
       </c>
       <c r="E8" t="n">
-        <v>13.03679818877306</v>
+        <v>18.14921078736153</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.428041120551498</v>
+        <v>1.561479207680579</v>
       </c>
       <c r="C9" t="n">
-        <v>7.464900476556104</v>
+        <v>10.98431814648328</v>
       </c>
       <c r="D9" t="n">
-        <v>6.349851430609814</v>
+        <v>7.70226322548758</v>
       </c>
       <c r="E9" t="n">
-        <v>15.24279302771742</v>
+        <v>20.24806057965144</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.709360650682955</v>
+        <v>0.9804910671853744</v>
       </c>
       <c r="C10" t="n">
-        <v>9.013470037843097</v>
+        <v>7.926837131106639</v>
       </c>
       <c r="D10" t="n">
-        <v>6.841598888913481</v>
+        <v>6.065983445092022</v>
       </c>
       <c r="E10" t="n">
-        <v>17.56442957743953</v>
+        <v>14.97331164338404</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.979131747531131</v>
+        <v>0.8885307597285759</v>
       </c>
       <c r="C11" t="n">
-        <v>10.61036057058638</v>
+        <v>8.702938143744872</v>
       </c>
       <c r="D11" t="n">
-        <v>7.362918347896128</v>
+        <v>5.928951100533252</v>
       </c>
       <c r="E11" t="n">
-        <v>19.95241066601364</v>
+        <v>15.5204200040067</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.242416856287321</v>
+        <v>0.9237362324028663</v>
       </c>
       <c r="C12" t="n">
-        <v>12.23309420350492</v>
+        <v>10.52644614708994</v>
       </c>
       <c r="D12" t="n">
-        <v>7.882255168208707</v>
+        <v>6.382106205859495</v>
       </c>
       <c r="E12" t="n">
-        <v>22.35776622800095</v>
+        <v>17.8322885853523</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.496182841995062</v>
+        <v>0.71026501159144</v>
       </c>
       <c r="C13" t="n">
-        <v>13.88413290469927</v>
+        <v>10.16620364449361</v>
       </c>
       <c r="D13" t="n">
-        <v>8.306129176852318</v>
+        <v>5.833908105285119</v>
       </c>
       <c r="E13" t="n">
-        <v>24.68644492354665</v>
+        <v>16.71037676137017</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.433135663705409</v>
+        <v>0.7438898704618931</v>
       </c>
       <c r="C14" t="n">
-        <v>9.699451333463552</v>
+        <v>12.03782710282382</v>
       </c>
       <c r="D14" t="n">
-        <v>6.293847087247706</v>
+        <v>6.266191254419073</v>
       </c>
       <c r="E14" t="n">
-        <v>17.42643408441667</v>
+        <v>19.04790822770478</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.456785965900715</v>
+        <v>0.6982091497832891</v>
       </c>
       <c r="C15" t="n">
-        <v>10.35134162656048</v>
+        <v>13.08479230706375</v>
       </c>
       <c r="D15" t="n">
-        <v>6.290577867392565</v>
+        <v>6.31677089614187</v>
       </c>
       <c r="E15" t="n">
-        <v>18.09870545985376</v>
+        <v>20.0997723529889</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.687575216215055</v>
+        <v>0.7469234708680159</v>
       </c>
       <c r="C16" t="n">
-        <v>12.08520624703077</v>
+        <v>15.21776682174149</v>
       </c>
       <c r="D16" t="n">
-        <v>6.767010210786499</v>
+        <v>6.763937340472208</v>
       </c>
       <c r="E16" t="n">
-        <v>20.53979167403232</v>
+        <v>22.72862763308172</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.357904337128976</v>
+        <v>0.4450065993809942</v>
       </c>
       <c r="C17" t="n">
-        <v>10.92864854656577</v>
+        <v>11.29927793987303</v>
       </c>
       <c r="D17" t="n">
-        <v>6.284451761718066</v>
+        <v>5.642339675755438</v>
       </c>
       <c r="E17" t="n">
-        <v>18.57100464541281</v>
+        <v>17.38662421500946</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.547352191617483</v>
+        <v>0.3386833230110646</v>
       </c>
       <c r="C18" t="n">
-        <v>12.61669500167887</v>
+        <v>10.2115800233839</v>
       </c>
       <c r="D18" t="n">
-        <v>6.683188591797907</v>
+        <v>5.186632026398153</v>
       </c>
       <c r="E18" t="n">
-        <v>20.84723578509426</v>
+        <v>15.73689537279312</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.550209077436841</v>
+        <v>0.38782961308566</v>
       </c>
       <c r="C19" t="n">
-        <v>13.38189861479996</v>
+        <v>12.5691980477474</v>
       </c>
       <c r="D19" t="n">
-        <v>6.777298926727006</v>
+        <v>5.686027448594421</v>
       </c>
       <c r="E19" t="n">
-        <v>21.7094066189638</v>
+        <v>18.64305510942749</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.72057175655479</v>
+        <v>0.4306043605596936</v>
       </c>
       <c r="C20" t="n">
-        <v>15.23491795413468</v>
+        <v>15.0582131848473</v>
       </c>
       <c r="D20" t="n">
-        <v>7.213410891907523</v>
+        <v>6.202613273092051</v>
       </c>
       <c r="E20" t="n">
-        <v>24.168900602597</v>
+        <v>21.69143081849904</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.020654365766112</v>
+        <v>0.4679598607062847</v>
       </c>
       <c r="C21" t="n">
-        <v>11.11503334821703</v>
+        <v>17.51843366178164</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018525761068732</v>
+        <v>6.640404026846833</v>
       </c>
       <c r="E21" t="n">
-        <v>18.15421347505188</v>
+        <v>24.62679754933475</v>
       </c>
     </row>
   </sheetData>
